--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532084</v>
+        <v>121532078</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458004</v>
+        <v>458405</v>
       </c>
       <c r="R2" t="n">
-        <v>7080451</v>
+        <v>7080225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532067</v>
+        <v>121532068</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457939</v>
+        <v>457941</v>
       </c>
       <c r="R3" t="n">
-        <v>7080589</v>
+        <v>7080592</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532075</v>
+        <v>121532066</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457972</v>
+        <v>457977</v>
       </c>
       <c r="R4" t="n">
-        <v>7079961</v>
+        <v>7080555</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121532089</v>
+        <v>121532069</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458166</v>
+        <v>457943</v>
       </c>
       <c r="R5" t="n">
-        <v>7080338</v>
+        <v>7080596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121532086</v>
+        <v>121532076</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458007</v>
+        <v>458073</v>
       </c>
       <c r="R6" t="n">
-        <v>7080540</v>
+        <v>7080127</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,7 +1213,7 @@
         <v>121532077</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121532088</v>
+        <v>121532070</v>
       </c>
       <c r="B8" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458245</v>
+        <v>457913</v>
       </c>
       <c r="R8" t="n">
-        <v>7080177</v>
+        <v>7080569</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121532070</v>
+        <v>121532085</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457913</v>
+        <v>458006</v>
       </c>
       <c r="R9" t="n">
-        <v>7080569</v>
+        <v>7080485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532073</v>
+        <v>121532088</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457982</v>
+        <v>458245</v>
       </c>
       <c r="R10" t="n">
-        <v>7080613</v>
+        <v>7080177</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532078</v>
+        <v>121532075</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458405</v>
+        <v>457972</v>
       </c>
       <c r="R11" t="n">
-        <v>7080225</v>
+        <v>7079961</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532068</v>
+        <v>121532082</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57466</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,20 +1747,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1758,17 +1768,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457941</v>
+        <v>458276</v>
       </c>
       <c r="R12" t="n">
-        <v>7080592</v>
+        <v>7080045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1827,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532092</v>
+        <v>121532089</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1869,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458219</v>
+        <v>458166</v>
       </c>
       <c r="R13" t="n">
-        <v>7080176</v>
+        <v>7080338</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1929,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121532082</v>
+        <v>121532073</v>
       </c>
       <c r="B14" t="n">
-        <v>57465</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,20 +1967,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1972,33 +1988,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458276</v>
+        <v>457982</v>
       </c>
       <c r="R14" t="n">
-        <v>7080045</v>
+        <v>7080613</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,6 +2031,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,7 +2065,7 @@
         <v>121532091</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121532074</v>
+        <v>121532084</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457993</v>
+        <v>458004</v>
       </c>
       <c r="R16" t="n">
-        <v>7080603</v>
+        <v>7080451</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,11 +2245,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121532069</v>
+        <v>121532074</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457943</v>
+        <v>457993</v>
       </c>
       <c r="R17" t="n">
-        <v>7080596</v>
+        <v>7080603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532093</v>
+        <v>121532087</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>90737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458475</v>
+        <v>458066</v>
       </c>
       <c r="R18" t="n">
-        <v>7080164</v>
+        <v>7080121</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,11 +2454,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532076</v>
+        <v>121532093</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,21 +2496,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458073</v>
+        <v>458475</v>
       </c>
       <c r="R19" t="n">
-        <v>7080127</v>
+        <v>7080164</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,7 +2560,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,10 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532087</v>
+        <v>121532067</v>
       </c>
       <c r="B20" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,21 +2603,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2632,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458066</v>
+        <v>457939</v>
       </c>
       <c r="R20" t="n">
-        <v>7080121</v>
+        <v>7080589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,6 +2663,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532085</v>
+        <v>121532092</v>
       </c>
       <c r="B21" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458006</v>
+        <v>458219</v>
       </c>
       <c r="R21" t="n">
-        <v>7080485</v>
+        <v>7080176</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2796,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532066</v>
+        <v>121532086</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,21 +2817,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457977</v>
+        <v>458007</v>
       </c>
       <c r="R22" t="n">
-        <v>7080555</v>
+        <v>7080540</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532082</v>
+        <v>121532089</v>
       </c>
       <c r="B12" t="n">
-        <v>57466</v>
+        <v>90737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,54 +1747,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458276</v>
+        <v>458166</v>
       </c>
       <c r="R12" t="n">
-        <v>7080045</v>
+        <v>7080338</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532089</v>
+        <v>121532082</v>
       </c>
       <c r="B13" t="n">
-        <v>90737</v>
+        <v>57466</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,38 +1849,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458166</v>
+        <v>458276</v>
       </c>
       <c r="R13" t="n">
-        <v>7080338</v>
+        <v>7080045</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532078</v>
+        <v>121532091</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458405</v>
+        <v>458038</v>
       </c>
       <c r="R2" t="n">
-        <v>7080225</v>
+        <v>7080052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532068</v>
+        <v>121532092</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457941</v>
+        <v>458219</v>
       </c>
       <c r="R3" t="n">
-        <v>7080592</v>
+        <v>7080176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532066</v>
+        <v>121532074</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457977</v>
+        <v>457993</v>
       </c>
       <c r="R4" t="n">
-        <v>7080555</v>
+        <v>7080603</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121532069</v>
+        <v>121532087</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457943</v>
+        <v>458066</v>
       </c>
       <c r="R5" t="n">
-        <v>7080596</v>
+        <v>7080121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121532076</v>
+        <v>121532069</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458073</v>
+        <v>457943</v>
       </c>
       <c r="R6" t="n">
-        <v>7080127</v>
+        <v>7080596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121532077</v>
+        <v>121532078</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458397</v>
+        <v>458405</v>
       </c>
       <c r="R7" t="n">
-        <v>7080262</v>
+        <v>7080225</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121532070</v>
+        <v>121532089</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457913</v>
+        <v>458166</v>
       </c>
       <c r="R8" t="n">
-        <v>7080569</v>
+        <v>7080338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121532085</v>
+        <v>121532068</v>
       </c>
       <c r="B9" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458006</v>
+        <v>457941</v>
       </c>
       <c r="R9" t="n">
-        <v>7080485</v>
+        <v>7080592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532088</v>
+        <v>121532070</v>
       </c>
       <c r="B10" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458245</v>
+        <v>457913</v>
       </c>
       <c r="R10" t="n">
-        <v>7080177</v>
+        <v>7080569</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532075</v>
+        <v>121532066</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457972</v>
+        <v>457977</v>
       </c>
       <c r="R11" t="n">
-        <v>7079961</v>
+        <v>7080555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532089</v>
+        <v>121532085</v>
       </c>
       <c r="B12" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458166</v>
+        <v>458006</v>
       </c>
       <c r="R12" t="n">
-        <v>7080338</v>
+        <v>7080485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1840,7 @@
         <v>121532082</v>
       </c>
       <c r="B13" t="n">
-        <v>57466</v>
+        <v>57467</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>121532073</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121532091</v>
+        <v>121532088</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458038</v>
+        <v>458245</v>
       </c>
       <c r="R15" t="n">
-        <v>7080052</v>
+        <v>7080177</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,11 +2138,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121532084</v>
+        <v>121532067</v>
       </c>
       <c r="B16" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458004</v>
+        <v>457939</v>
       </c>
       <c r="R16" t="n">
-        <v>7080451</v>
+        <v>7080589</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,6 +2240,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121532074</v>
+        <v>121532084</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457993</v>
+        <v>458004</v>
       </c>
       <c r="R17" t="n">
-        <v>7080603</v>
+        <v>7080451</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2347,11 +2347,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532087</v>
+        <v>121532093</v>
       </c>
       <c r="B18" t="n">
-        <v>90737</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,21 +2389,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458066</v>
+        <v>458475</v>
       </c>
       <c r="R18" t="n">
-        <v>7080121</v>
+        <v>7080164</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2449,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532093</v>
+        <v>121532076</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458475</v>
+        <v>458073</v>
       </c>
       <c r="R19" t="n">
-        <v>7080164</v>
+        <v>7080127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,10 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532067</v>
+        <v>121532077</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457939</v>
+        <v>458397</v>
       </c>
       <c r="R20" t="n">
-        <v>7080589</v>
+        <v>7080262</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532092</v>
+        <v>121532075</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458219</v>
+        <v>457972</v>
       </c>
       <c r="R21" t="n">
-        <v>7080176</v>
+        <v>7079961</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2804,7 +2804,7 @@
         <v>121532086</v>
       </c>
       <c r="B22" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532091</v>
+        <v>121532088</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458038</v>
+        <v>458245</v>
       </c>
       <c r="R2" t="n">
-        <v>7080052</v>
+        <v>7080177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532092</v>
+        <v>121532073</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458219</v>
+        <v>457982</v>
       </c>
       <c r="R3" t="n">
-        <v>7080176</v>
+        <v>7080613</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532074</v>
+        <v>121532082</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,17 +917,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457993</v>
+        <v>458276</v>
       </c>
       <c r="R4" t="n">
-        <v>7080603</v>
+        <v>7080045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +976,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121532087</v>
+        <v>121532074</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458066</v>
+        <v>457993</v>
       </c>
       <c r="R5" t="n">
-        <v>7080121</v>
+        <v>7080603</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121532069</v>
+        <v>121532077</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1138,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457943</v>
+        <v>458397</v>
       </c>
       <c r="R6" t="n">
-        <v>7080596</v>
+        <v>7080262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121532078</v>
+        <v>121532070</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1245,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458405</v>
+        <v>457913</v>
       </c>
       <c r="R7" t="n">
-        <v>7080225</v>
+        <v>7080569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121532089</v>
+        <v>121532087</v>
       </c>
       <c r="B8" t="n">
         <v>90738</v>
@@ -1352,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458166</v>
+        <v>458066</v>
       </c>
       <c r="R8" t="n">
-        <v>7080338</v>
+        <v>7080121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1521,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532070</v>
+        <v>121532076</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1561,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457913</v>
+        <v>458073</v>
       </c>
       <c r="R10" t="n">
-        <v>7080569</v>
+        <v>7080127</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1612,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532066</v>
+        <v>121532086</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457977</v>
+        <v>458007</v>
       </c>
       <c r="R11" t="n">
-        <v>7080555</v>
+        <v>7080540</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532085</v>
+        <v>121532067</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458006</v>
+        <v>457939</v>
       </c>
       <c r="R12" t="n">
-        <v>7080485</v>
+        <v>7080589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1817,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532082</v>
+        <v>121532092</v>
       </c>
       <c r="B13" t="n">
-        <v>57467</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1849,54 +1860,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458276</v>
+        <v>458219</v>
       </c>
       <c r="R13" t="n">
-        <v>7080045</v>
+        <v>7080176</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,6 +1924,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,7 +1955,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121532073</v>
+        <v>121532069</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457982</v>
+        <v>457943</v>
       </c>
       <c r="R14" t="n">
-        <v>7080613</v>
+        <v>7080596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121532088</v>
+        <v>121532075</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458245</v>
+        <v>457972</v>
       </c>
       <c r="R15" t="n">
-        <v>7080177</v>
+        <v>7079961</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,6 +2138,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121532067</v>
+        <v>121532089</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457939</v>
+        <v>458166</v>
       </c>
       <c r="R16" t="n">
-        <v>7080589</v>
+        <v>7080338</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,11 +2245,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121532084</v>
+        <v>121532093</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458004</v>
+        <v>458475</v>
       </c>
       <c r="R17" t="n">
-        <v>7080451</v>
+        <v>7080164</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2347,6 +2347,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,10 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532093</v>
+        <v>121532084</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,21 +2394,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2418,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458475</v>
+        <v>458004</v>
       </c>
       <c r="R18" t="n">
-        <v>7080164</v>
+        <v>7080451</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,11 +2454,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532076</v>
+        <v>121532091</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458073</v>
+        <v>458038</v>
       </c>
       <c r="R19" t="n">
-        <v>7080127</v>
+        <v>7080052</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,10 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532077</v>
+        <v>121532085</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,21 +2603,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458397</v>
+        <v>458006</v>
       </c>
       <c r="R20" t="n">
-        <v>7080262</v>
+        <v>7080485</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,11 +2663,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,7 +2689,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532075</v>
+        <v>121532066</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2734,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457972</v>
+        <v>457977</v>
       </c>
       <c r="R21" t="n">
-        <v>7079961</v>
+        <v>7080555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,7 +2769,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532086</v>
+        <v>121532078</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,21 +2812,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458007</v>
+        <v>458405</v>
       </c>
       <c r="R22" t="n">
-        <v>7080540</v>
+        <v>7080225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532088</v>
+        <v>121532068</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458245</v>
+        <v>457941</v>
       </c>
       <c r="R2" t="n">
-        <v>7080177</v>
+        <v>7080592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532073</v>
+        <v>121532086</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457982</v>
+        <v>458007</v>
       </c>
       <c r="R3" t="n">
-        <v>7080613</v>
+        <v>7080540</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532082</v>
+        <v>121532067</v>
       </c>
       <c r="B4" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -917,33 +917,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458276</v>
+        <v>457939</v>
       </c>
       <c r="R4" t="n">
-        <v>7080045</v>
+        <v>7080589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121532074</v>
+        <v>121532073</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1042,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457993</v>
+        <v>457982</v>
       </c>
       <c r="R5" t="n">
-        <v>7080603</v>
+        <v>7080613</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121532077</v>
+        <v>121532070</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1149,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458397</v>
+        <v>457913</v>
       </c>
       <c r="R6" t="n">
-        <v>7080262</v>
+        <v>7080569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121532070</v>
+        <v>121532069</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1256,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457913</v>
+        <v>457943</v>
       </c>
       <c r="R7" t="n">
-        <v>7080569</v>
+        <v>7080596</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121532087</v>
+        <v>121532076</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458066</v>
+        <v>458073</v>
       </c>
       <c r="R8" t="n">
-        <v>7080121</v>
+        <v>7080127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121532068</v>
+        <v>121532074</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1465,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457941</v>
+        <v>457993</v>
       </c>
       <c r="R9" t="n">
-        <v>7080592</v>
+        <v>7080603</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532076</v>
+        <v>121532078</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1572,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458073</v>
+        <v>458405</v>
       </c>
       <c r="R10" t="n">
-        <v>7080127</v>
+        <v>7080225</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532086</v>
+        <v>121532082</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>57467</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,38 +1645,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458007</v>
+        <v>458276</v>
       </c>
       <c r="R11" t="n">
-        <v>7080540</v>
+        <v>7080045</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,10 +1751,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532067</v>
+        <v>121532087</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457939</v>
+        <v>458066</v>
       </c>
       <c r="R12" t="n">
-        <v>7080589</v>
+        <v>7080121</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,11 +1827,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532092</v>
+        <v>121532088</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,21 +1869,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1888,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458219</v>
+        <v>458245</v>
       </c>
       <c r="R13" t="n">
-        <v>7080176</v>
+        <v>7080177</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,11 +1929,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121532069</v>
+        <v>121532089</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457943</v>
+        <v>458166</v>
       </c>
       <c r="R14" t="n">
-        <v>7080596</v>
+        <v>7080338</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,11 +2031,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121532075</v>
+        <v>121532084</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457972</v>
+        <v>458004</v>
       </c>
       <c r="R15" t="n">
-        <v>7079961</v>
+        <v>7080451</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,11 +2133,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121532089</v>
+        <v>121532066</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458166</v>
+        <v>457977</v>
       </c>
       <c r="R16" t="n">
-        <v>7080338</v>
+        <v>7080555</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,6 +2235,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,7 +2266,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121532093</v>
+        <v>121532091</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2311,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458475</v>
+        <v>458038</v>
       </c>
       <c r="R17" t="n">
-        <v>7080164</v>
+        <v>7080052</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532084</v>
+        <v>121532077</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,21 +2389,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458004</v>
+        <v>458397</v>
       </c>
       <c r="R18" t="n">
-        <v>7080451</v>
+        <v>7080262</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,6 +2449,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532091</v>
+        <v>121532075</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458038</v>
+        <v>457972</v>
       </c>
       <c r="R19" t="n">
-        <v>7080052</v>
+        <v>7079961</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,10 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532085</v>
+        <v>121532093</v>
       </c>
       <c r="B20" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,21 +2603,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458006</v>
+        <v>458475</v>
       </c>
       <c r="R20" t="n">
-        <v>7080485</v>
+        <v>7080164</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,6 +2663,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2689,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532066</v>
+        <v>121532085</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457977</v>
+        <v>458006</v>
       </c>
       <c r="R21" t="n">
-        <v>7080555</v>
+        <v>7080485</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,11 +2770,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532078</v>
+        <v>121532092</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,21 +2812,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458405</v>
+        <v>458219</v>
       </c>
       <c r="R22" t="n">
-        <v>7080225</v>
+        <v>7080176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532068</v>
+        <v>121532093</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457941</v>
+        <v>458475</v>
       </c>
       <c r="R2" t="n">
-        <v>7080592</v>
+        <v>7080164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532086</v>
+        <v>121532085</v>
       </c>
       <c r="B3" t="n">
         <v>90738</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458007</v>
+        <v>458006</v>
       </c>
       <c r="R3" t="n">
-        <v>7080540</v>
+        <v>7080485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532067</v>
+        <v>121532091</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457939</v>
+        <v>458038</v>
       </c>
       <c r="R4" t="n">
-        <v>7080589</v>
+        <v>7080052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121532073</v>
+        <v>121532082</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,20 +1003,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,17 +1024,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457982</v>
+        <v>458276</v>
       </c>
       <c r="R5" t="n">
-        <v>7080613</v>
+        <v>7080045</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1083,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121532070</v>
+        <v>121532074</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1138,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457913</v>
+        <v>457993</v>
       </c>
       <c r="R6" t="n">
-        <v>7080569</v>
+        <v>7080603</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1189,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121532069</v>
+        <v>121532086</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1232,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457943</v>
+        <v>458007</v>
       </c>
       <c r="R7" t="n">
-        <v>7080596</v>
+        <v>7080540</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1292,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121532076</v>
+        <v>121532084</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1334,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458073</v>
+        <v>458004</v>
       </c>
       <c r="R8" t="n">
-        <v>7080127</v>
+        <v>7080451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1394,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1420,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121532074</v>
+        <v>121532066</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1459,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457993</v>
+        <v>457977</v>
       </c>
       <c r="R9" t="n">
-        <v>7080603</v>
+        <v>7080555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1500,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532078</v>
+        <v>121532067</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458405</v>
+        <v>457939</v>
       </c>
       <c r="R10" t="n">
-        <v>7080225</v>
+        <v>7080589</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532082</v>
+        <v>121532070</v>
       </c>
       <c r="B11" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,20 +1646,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1666,33 +1667,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458276</v>
+        <v>457913</v>
       </c>
       <c r="R11" t="n">
-        <v>7080045</v>
+        <v>7080569</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,6 +1710,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532087</v>
+        <v>121532075</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1791,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458066</v>
+        <v>457972</v>
       </c>
       <c r="R12" t="n">
-        <v>7080121</v>
+        <v>7079961</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,6 +1817,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532088</v>
+        <v>121532092</v>
       </c>
       <c r="B13" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,21 +1864,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458245</v>
+        <v>458219</v>
       </c>
       <c r="R13" t="n">
-        <v>7080177</v>
+        <v>7080176</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,6 +1924,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,7 +1955,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121532089</v>
+        <v>121532087</v>
       </c>
       <c r="B14" t="n">
         <v>90738</v>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458166</v>
+        <v>458066</v>
       </c>
       <c r="R14" t="n">
-        <v>7080338</v>
+        <v>7080121</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121532084</v>
+        <v>121532089</v>
       </c>
       <c r="B15" t="n">
         <v>90738</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458004</v>
+        <v>458166</v>
       </c>
       <c r="R15" t="n">
-        <v>7080451</v>
+        <v>7080338</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121532066</v>
+        <v>121532073</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457977</v>
+        <v>457982</v>
       </c>
       <c r="R16" t="n">
-        <v>7080555</v>
+        <v>7080613</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121532091</v>
+        <v>121532068</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458038</v>
+        <v>457941</v>
       </c>
       <c r="R17" t="n">
-        <v>7080052</v>
+        <v>7080592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,7 +2373,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532077</v>
+        <v>121532078</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458397</v>
+        <v>458405</v>
       </c>
       <c r="R18" t="n">
-        <v>7080262</v>
+        <v>7080225</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532075</v>
+        <v>121532076</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457972</v>
+        <v>458073</v>
       </c>
       <c r="R19" t="n">
-        <v>7079961</v>
+        <v>7080127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,10 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532093</v>
+        <v>121532069</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,21 +2603,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458475</v>
+        <v>457943</v>
       </c>
       <c r="R20" t="n">
-        <v>7080164</v>
+        <v>7080596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532085</v>
+        <v>121532077</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458006</v>
+        <v>458397</v>
       </c>
       <c r="R21" t="n">
-        <v>7080485</v>
+        <v>7080262</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2796,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532092</v>
+        <v>121532088</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,21 +2817,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458219</v>
+        <v>458245</v>
       </c>
       <c r="R22" t="n">
-        <v>7080176</v>
+        <v>7080177</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532085</v>
+        <v>121532091</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458006</v>
+        <v>458038</v>
       </c>
       <c r="R3" t="n">
-        <v>7080485</v>
+        <v>7080052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532091</v>
+        <v>121532085</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458038</v>
+        <v>458006</v>
       </c>
       <c r="R4" t="n">
-        <v>7080052</v>
+        <v>7080485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532067</v>
+        <v>121532092</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,21 +1543,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457939</v>
+        <v>458219</v>
       </c>
       <c r="R10" t="n">
-        <v>7080589</v>
+        <v>7080176</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,7 +1634,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532070</v>
+        <v>121532067</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457913</v>
+        <v>457939</v>
       </c>
       <c r="R11" t="n">
-        <v>7080569</v>
+        <v>7080589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532075</v>
+        <v>121532070</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457972</v>
+        <v>457913</v>
       </c>
       <c r="R12" t="n">
-        <v>7079961</v>
+        <v>7080569</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532092</v>
+        <v>121532075</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,21 +1864,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458219</v>
+        <v>457972</v>
       </c>
       <c r="R13" t="n">
-        <v>7080176</v>
+        <v>7079961</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532093</v>
+        <v>121532074</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458475</v>
+        <v>457993</v>
       </c>
       <c r="R2" t="n">
-        <v>7080164</v>
+        <v>7080603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532091</v>
+        <v>121532088</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458038</v>
+        <v>458245</v>
       </c>
       <c r="R3" t="n">
-        <v>7080052</v>
+        <v>7080177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532085</v>
+        <v>121532089</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458006</v>
+        <v>458166</v>
       </c>
       <c r="R4" t="n">
-        <v>7080485</v>
+        <v>7080338</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121532082</v>
+        <v>121532078</v>
       </c>
       <c r="B5" t="n">
-        <v>57467</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,20 +998,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,33 +1019,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458276</v>
+        <v>458405</v>
       </c>
       <c r="R5" t="n">
-        <v>7080045</v>
+        <v>7080225</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121532074</v>
+        <v>121532068</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457993</v>
+        <v>457941</v>
       </c>
       <c r="R6" t="n">
-        <v>7080603</v>
+        <v>7080592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121532086</v>
+        <v>121532075</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458007</v>
+        <v>457972</v>
       </c>
       <c r="R7" t="n">
-        <v>7080540</v>
+        <v>7079961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121532084</v>
+        <v>121532067</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458004</v>
+        <v>457939</v>
       </c>
       <c r="R8" t="n">
-        <v>7080451</v>
+        <v>7080589</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121532066</v>
+        <v>121532084</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457977</v>
+        <v>458004</v>
       </c>
       <c r="R9" t="n">
-        <v>7080555</v>
+        <v>7080451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532092</v>
+        <v>121532093</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458219</v>
+        <v>458475</v>
       </c>
       <c r="R10" t="n">
-        <v>7080176</v>
+        <v>7080164</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532067</v>
+        <v>121532076</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457939</v>
+        <v>458073</v>
       </c>
       <c r="R11" t="n">
-        <v>7080589</v>
+        <v>7080127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532070</v>
+        <v>121532073</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457913</v>
+        <v>457982</v>
       </c>
       <c r="R12" t="n">
-        <v>7080569</v>
+        <v>7080613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532075</v>
+        <v>121532069</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457972</v>
+        <v>457943</v>
       </c>
       <c r="R13" t="n">
-        <v>7079961</v>
+        <v>7080596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121532087</v>
+        <v>121532086</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458066</v>
+        <v>458007</v>
       </c>
       <c r="R14" t="n">
-        <v>7080121</v>
+        <v>7080540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121532089</v>
+        <v>121532070</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2073,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458166</v>
+        <v>457913</v>
       </c>
       <c r="R15" t="n">
-        <v>7080338</v>
+        <v>7080569</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2159,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121532073</v>
+        <v>121532085</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457982</v>
+        <v>458006</v>
       </c>
       <c r="R16" t="n">
-        <v>7080613</v>
+        <v>7080485</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,11 +2229,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2266,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121532068</v>
+        <v>121532077</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457941</v>
+        <v>458397</v>
       </c>
       <c r="R17" t="n">
-        <v>7080592</v>
+        <v>7080262</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532078</v>
+        <v>121532066</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2413,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458405</v>
+        <v>457977</v>
       </c>
       <c r="R18" t="n">
-        <v>7080225</v>
+        <v>7080555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532076</v>
+        <v>121532091</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2520,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458073</v>
+        <v>458038</v>
       </c>
       <c r="R19" t="n">
-        <v>7080127</v>
+        <v>7080052</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,7 +2549,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532069</v>
+        <v>121532087</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2627,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457943</v>
+        <v>458066</v>
       </c>
       <c r="R20" t="n">
-        <v>7080596</v>
+        <v>7080121</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,11 +2652,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532077</v>
+        <v>121532092</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458397</v>
+        <v>458219</v>
       </c>
       <c r="R21" t="n">
-        <v>7080262</v>
+        <v>7080176</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,7 +2758,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532088</v>
+        <v>121532082</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>57468</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2813,38 +2797,54 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458245</v>
+        <v>458276</v>
       </c>
       <c r="R22" t="n">
-        <v>7080177</v>
+        <v>7080045</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532076</v>
+        <v>121532089</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458073</v>
+        <v>458166</v>
       </c>
       <c r="R2" t="n">
-        <v>7080127</v>
+        <v>7080338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532067</v>
+        <v>121532088</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457939</v>
+        <v>458245</v>
       </c>
       <c r="R3" t="n">
-        <v>7080589</v>
+        <v>7080177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532075</v>
+        <v>121532092</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457972</v>
+        <v>458219</v>
       </c>
       <c r="R4" t="n">
-        <v>7079961</v>
+        <v>7080176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121532077</v>
+        <v>121532084</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458397</v>
+        <v>458004</v>
       </c>
       <c r="R5" t="n">
-        <v>7080262</v>
+        <v>7080451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121532082</v>
+        <v>121532076</v>
       </c>
       <c r="B6" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,20 +1100,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1136,33 +1121,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458276</v>
+        <v>458073</v>
       </c>
       <c r="R6" t="n">
-        <v>7080045</v>
+        <v>7080127</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121532084</v>
+        <v>121532069</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458004</v>
+        <v>457943</v>
       </c>
       <c r="R7" t="n">
-        <v>7080451</v>
+        <v>7080596</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121532073</v>
+        <v>121532086</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457982</v>
+        <v>458007</v>
       </c>
       <c r="R8" t="n">
-        <v>7080613</v>
+        <v>7080540</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121532085</v>
+        <v>121532073</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458006</v>
+        <v>457982</v>
       </c>
       <c r="R9" t="n">
-        <v>7080485</v>
+        <v>7080613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532074</v>
+        <v>121532067</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1679,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457993</v>
+        <v>457939</v>
       </c>
       <c r="R11" t="n">
-        <v>7080603</v>
+        <v>7080589</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532078</v>
+        <v>121532066</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1786,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458405</v>
+        <v>457977</v>
       </c>
       <c r="R12" t="n">
-        <v>7080225</v>
+        <v>7080555</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532086</v>
+        <v>121532091</v>
       </c>
       <c r="B13" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458007</v>
+        <v>458038</v>
       </c>
       <c r="R13" t="n">
-        <v>7080540</v>
+        <v>7080052</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121532091</v>
+        <v>121532082</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57468</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,38 +1951,54 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458038</v>
+        <v>458276</v>
       </c>
       <c r="R14" t="n">
-        <v>7080052</v>
+        <v>7080045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,11 +2031,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121532093</v>
+        <v>121532074</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458475</v>
+        <v>457993</v>
       </c>
       <c r="R15" t="n">
-        <v>7080164</v>
+        <v>7080603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,7 +2137,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2169,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121532089</v>
+        <v>121532075</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458166</v>
+        <v>457972</v>
       </c>
       <c r="R16" t="n">
-        <v>7080338</v>
+        <v>7079961</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,6 +2240,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121532092</v>
+        <v>121532078</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458219</v>
+        <v>458405</v>
       </c>
       <c r="R17" t="n">
-        <v>7080176</v>
+        <v>7080225</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,10 +2378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532066</v>
+        <v>121532093</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457977</v>
+        <v>458475</v>
       </c>
       <c r="R18" t="n">
-        <v>7080555</v>
+        <v>7080164</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532068</v>
+        <v>121532087</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,21 +2501,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457941</v>
+        <v>458066</v>
       </c>
       <c r="R19" t="n">
-        <v>7080592</v>
+        <v>7080121</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,11 +2561,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,7 +2587,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532069</v>
+        <v>121532068</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2632,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457943</v>
+        <v>457941</v>
       </c>
       <c r="R20" t="n">
-        <v>7080596</v>
+        <v>7080592</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532087</v>
+        <v>121532077</v>
       </c>
       <c r="B21" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458066</v>
+        <v>458397</v>
       </c>
       <c r="R21" t="n">
-        <v>7080121</v>
+        <v>7080262</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,6 +2770,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,7 +2801,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532088</v>
+        <v>121532085</v>
       </c>
       <c r="B22" t="n">
         <v>90746</v>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458245</v>
+        <v>458006</v>
       </c>
       <c r="R22" t="n">
-        <v>7080177</v>
+        <v>7080485</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121532082</v>
+        <v>121532074</v>
       </c>
       <c r="B14" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,20 +1951,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1972,33 +1972,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458276</v>
+        <v>457993</v>
       </c>
       <c r="R14" t="n">
-        <v>7080045</v>
+        <v>7080603</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,6 +2015,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121532074</v>
+        <v>121532082</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,20 +2058,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2090,17 +2079,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457993</v>
+        <v>458276</v>
       </c>
       <c r="R15" t="n">
-        <v>7080603</v>
+        <v>7080045</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,11 +2138,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 54427-2024 artfynd.xlsx
+++ b/artfynd/A 54427-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532089</v>
+        <v>121532088</v>
       </c>
       <c r="B2" t="n">
         <v>90746</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458166</v>
+        <v>458245</v>
       </c>
       <c r="R2" t="n">
-        <v>7080338</v>
+        <v>7080177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532088</v>
+        <v>121532085</v>
       </c>
       <c r="B3" t="n">
         <v>90746</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458245</v>
+        <v>458006</v>
       </c>
       <c r="R3" t="n">
-        <v>7080177</v>
+        <v>7080485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532092</v>
+        <v>121532084</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458219</v>
+        <v>458004</v>
       </c>
       <c r="R4" t="n">
-        <v>7080176</v>
+        <v>7080451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121532084</v>
+        <v>121532091</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458004</v>
+        <v>458038</v>
       </c>
       <c r="R5" t="n">
-        <v>7080451</v>
+        <v>7080052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121532076</v>
+        <v>121532077</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458073</v>
+        <v>458397</v>
       </c>
       <c r="R6" t="n">
-        <v>7080127</v>
+        <v>7080262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121532069</v>
+        <v>121532070</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457943</v>
+        <v>457913</v>
       </c>
       <c r="R7" t="n">
-        <v>7080596</v>
+        <v>7080569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121532086</v>
+        <v>121532066</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458007</v>
+        <v>457977</v>
       </c>
       <c r="R8" t="n">
-        <v>7080540</v>
+        <v>7080555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121532073</v>
+        <v>121532082</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,20 +1421,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1437,17 +1442,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457982</v>
+        <v>458276</v>
       </c>
       <c r="R9" t="n">
-        <v>7080613</v>
+        <v>7080045</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1501,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532070</v>
+        <v>121532078</v>
       </c>
       <c r="B10" t="n">
         <v>57357</v>
@@ -1551,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457913</v>
+        <v>458405</v>
       </c>
       <c r="R10" t="n">
-        <v>7080569</v>
+        <v>7080225</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121532067</v>
+        <v>121532092</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457939</v>
+        <v>458219</v>
       </c>
       <c r="R11" t="n">
-        <v>7080589</v>
+        <v>7080176</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1714,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1741,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121532066</v>
+        <v>121532073</v>
       </c>
       <c r="B12" t="n">
         <v>57357</v>
@@ -1765,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457977</v>
+        <v>457982</v>
       </c>
       <c r="R12" t="n">
-        <v>7080555</v>
+        <v>7080613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121532091</v>
+        <v>121532068</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1864,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458038</v>
+        <v>457941</v>
       </c>
       <c r="R13" t="n">
-        <v>7080052</v>
+        <v>7080592</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1928,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1955,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121532074</v>
+        <v>121532069</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -1979,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457993</v>
+        <v>457943</v>
       </c>
       <c r="R14" t="n">
-        <v>7080603</v>
+        <v>7080596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2035,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121532082</v>
+        <v>121532074</v>
       </c>
       <c r="B15" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,20 +2074,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2079,33 +2095,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458276</v>
+        <v>457993</v>
       </c>
       <c r="R15" t="n">
-        <v>7080045</v>
+        <v>7080603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,6 +2138,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121532075</v>
+        <v>121532093</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457972</v>
+        <v>458475</v>
       </c>
       <c r="R16" t="n">
-        <v>7079961</v>
+        <v>7080164</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,7 +2249,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,7 +2276,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121532078</v>
+        <v>121532067</v>
       </c>
       <c r="B17" t="n">
         <v>57357</v>
@@ -2311,10 +2316,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458405</v>
+        <v>457939</v>
       </c>
       <c r="R17" t="n">
-        <v>7080225</v>
+        <v>7080589</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,10 +2383,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121532093</v>
+        <v>121532087</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,21 +2399,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2418,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458475</v>
+        <v>458066</v>
       </c>
       <c r="R18" t="n">
-        <v>7080164</v>
+        <v>7080121</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,11 +2459,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,7 +2485,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121532087</v>
+        <v>121532089</v>
       </c>
       <c r="B19" t="n">
         <v>90746</v>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458066</v>
+        <v>458166</v>
       </c>
       <c r="R19" t="n">
-        <v>7080121</v>
+        <v>7080338</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121532068</v>
+        <v>121532075</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457941</v>
+        <v>457972</v>
       </c>
       <c r="R20" t="n">
-        <v>7080592</v>
+        <v>7079961</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121532077</v>
+        <v>121532076</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458397</v>
+        <v>458073</v>
       </c>
       <c r="R21" t="n">
-        <v>7080262</v>
+        <v>7080127</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,7 +2801,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121532085</v>
+        <v>121532086</v>
       </c>
       <c r="B22" t="n">
         <v>90746</v>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458006</v>
+        <v>458007</v>
       </c>
       <c r="R22" t="n">
-        <v>7080485</v>
+        <v>7080540</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
